--- a/backend/data/financials_by_company/000534.SZ.xlsx
+++ b/backend/data/financials_by_company/000534.SZ.xlsx
@@ -4019,197 +4019,197 @@
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="EW1" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Wedge Industrial Co.,Ltd., together with its subsidiaries, engages in the research and development, production, and sale of micro-ecological live bacteria products, superalloys, and related products in China. The company offers micro-ecological preparations, such as bifidobacterium lactobacillus triple live bacteria tablets under the Golden Bifidobacterium brand; vaginal lactobacillus live capsules under the Dingjunsheng brand; dual-span microecological live bacteria drugs under the Jinshuangqi brand; and vaginal microecological live bacteria drug for use in the treatment of gynecological infections under the Dingjunsheng brand. It also provides probiotic products, health food products, probiotic dietary supplements, probiotic hand creams, and other probiotic health products under the Sanlian Probiotics, Bacteria powder, and Today's Bacteria brands. In addition, the company is involved in the research, development, and manufacture of high-temperature alloy materials and core components, including precision casting blades, high temperature alloy powder discs, high temperature master alloys and their alloy powders, and nickel-based high-temperature master alloys. Wedge Industrial Co.,Ltd. was formerly known as Guangdong Wanze Industrial Co., Ltd. and changed its name to Wedge Industrial Co., Ltd. in May 2013. The company was founded in 1992 and is based in Shantou, China.</t>
+          <t>Wedge Industrial Co.,Ltd., together with its subsidiaries, engages in the research and development, production, and sale of micro-ecological live bacteria products, superalloys, and related products in China. It offers microecological preparations, such as bifidobacterium lactobacillus triple live bacteria tablets under the Golden Bifidobacterium brand; vaginal lactobacillus live capsules under the Dingjun Sheng brand; dual-span microecological live bacteria drugs under the Jin Shuangqi brand; and vaginal microecological live bacteria drug for use in the treatment of gynecological infections under the Dingjunsheng brand. The company also provides probiotic products, health food products, probiotic dietary supplements, probiotic hand creams, and other probiotic health products under the Sanlian Probiotics, Bacteria powder, and Today's Bacteria brands. In addition, it is involved in the research, development, and manufacture of high-temperature alloy materials and core components, including precision casting blades, high temperature alloy powder discs, high temperature master alloys and their alloy powders, and nickel-based high-temperature master alloys. The company was formerly known as Guangdong Wanze Industrial Co., Ltd. and changed its name to Wedge Industrial Co., Ltd. in May 2013. The company was founded in 1992 and is based in Shantou, China.</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4314,28 +4314,28 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>32.36</v>
+        <v>30.38</v>
       </c>
       <c r="V2" t="n">
-        <v>29.88</v>
+        <v>28.66</v>
       </c>
       <c r="W2" t="n">
-        <v>30.72</v>
+        <v>30.39</v>
       </c>
       <c r="X2" t="n">
-        <v>33.08</v>
+        <v>33.19</v>
       </c>
       <c r="Y2" t="n">
-        <v>32.36</v>
+        <v>30.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>29.88</v>
+        <v>28.66</v>
       </c>
       <c r="AA2" t="n">
-        <v>30.72</v>
+        <v>30.39</v>
       </c>
       <c r="AB2" t="n">
-        <v>33.08</v>
+        <v>33.19</v>
       </c>
       <c r="AC2" t="n">
         <v>0.05</v>
@@ -4353,34 +4353,34 @@
         <v>0.46</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.449</v>
+        <v>0.471</v>
       </c>
       <c r="AI2" t="n">
-        <v>78.84999999999999</v>
+        <v>80.02499400000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>37.10588</v>
+        <v>37.65882</v>
       </c>
       <c r="AK2" t="n">
-        <v>31416990</v>
+        <v>29218314</v>
       </c>
       <c r="AL2" t="n">
-        <v>31416990</v>
+        <v>29218314</v>
       </c>
       <c r="AM2" t="n">
-        <v>24309840</v>
+        <v>24424981</v>
       </c>
       <c r="AN2" t="n">
-        <v>21229311</v>
+        <v>22332288</v>
       </c>
       <c r="AO2" t="n">
-        <v>21229311</v>
+        <v>22332288</v>
       </c>
       <c r="AP2" t="n">
-        <v>31.51</v>
+        <v>32.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>31.53</v>
+        <v>32.04</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>16071160832</v>
+        <v>16310646784</v>
       </c>
       <c r="AU2" t="n">
-        <v>16488989977</v>
+        <v>14960344429</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.91</v>
+        <v>14.11</v>
       </c>
       <c r="AW2" t="n">
         <v>49.14</v>
@@ -4407,13 +4407,13 @@
         <v>1.312867</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.219128</v>
+        <v>12.401212</v>
       </c>
       <c r="BA2" t="n">
-        <v>37.3358</v>
+        <v>34.68</v>
       </c>
       <c r="BB2" t="n">
-        <v>28.55335</v>
+        <v>29.1454</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
@@ -4430,13 +4430,13 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>17117303808</v>
+        <v>17344008192</v>
       </c>
       <c r="BH2" t="n">
         <v>0.15343</v>
       </c>
       <c r="BI2" t="n">
-        <v>332620540</v>
+        <v>296704583</v>
       </c>
       <c r="BJ2" t="n">
         <v>509548516</v>
@@ -4445,7 +4445,7 @@
         <v>0.29801</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.22618</v>
+        <v>0.22634001</v>
       </c>
       <c r="BM2" t="n">
         <v>509548516</v>
@@ -4454,7 +4454,7 @@
         <v>3.561</v>
       </c>
       <c r="BO2" t="n">
-        <v>8.857062000000001</v>
+        <v>8.989046999999999</v>
       </c>
       <c r="BP2" t="n">
         <v>1767139200</v>
@@ -4489,16 +4489,16 @@
         <v>1155254400</v>
       </c>
       <c r="BZ2" t="n">
-        <v>13.015</v>
+        <v>13.187</v>
       </c>
       <c r="CA2" t="n">
-        <v>62.234</v>
+        <v>63.058</v>
       </c>
       <c r="CB2" t="n">
-        <v>1.4796934</v>
+        <v>1.0402956</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CD2" t="n">
         <v>0.05</v>
@@ -4512,7 +4512,7 @@
         </is>
       </c>
       <c r="CG2" t="n">
-        <v>31.54</v>
+        <v>32.01</v>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
@@ -4614,90 +4614,102 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
-        <v>31.54</v>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DK2" t="n">
-        <v>-0.8199997</v>
+        <v>1783062255</v>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>30.72 - 33.08</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>24309840</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>18.630001</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1.4430674</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>12.91 - 49.14</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>-17.599998</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.35816032</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>147.96935</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1619693940</v>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>finmb_20359588</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>Wedge Industrial Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>WEDGE INDUSTRIAL CO LTD</t>
+        </is>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>1619693940</v>
+        <v>0.4</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.85</v>
+        <v>-2.670002</v>
       </c>
       <c r="DY2" t="n">
-        <v>-5.7957993</v>
+        <v>-0.07698967</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.15523437</v>
+        <v>2.8645992</v>
       </c>
       <c r="EA2" t="n">
-        <v>2.9866505</v>
+        <v>0.0982865</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.10459895</v>
+        <v>15</v>
       </c>
       <c r="EC2" t="n">
         <v>15</v>
       </c>
-      <c r="ED2" t="n">
-        <v>15</v>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>Wedge Industrial Co., Ltd.</t>
+        </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>Wedge Industrial Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="EG2" t="b">
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="EF2" t="b">
         <v>0</v>
       </c>
-      <c r="EH2" t="b">
-        <v>0</v>
+      <c r="EG2" t="n">
+        <v>5.3653693</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>32.01</v>
       </c>
       <c r="EI2" t="b">
         <v>0</v>
@@ -4705,59 +4717,47 @@
       <c r="EJ2" t="n">
         <v>758165400000</v>
       </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>Wedge Industrial Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="EL2" t="n">
-        <v>-2.5339916</v>
+      <c r="EK2" t="n">
+        <v>1.6299992</v>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>30.39 - 33.19</t>
+        </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>finmb_20359588</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EQ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="EN2" t="n">
+        <v>24424981</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>17.899998</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1.2686037</v>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>14.11 - 49.14</t>
+        </is>
+      </c>
+      <c r="ER2" t="n">
+        <v>-17.130001</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>-0.3485959</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>104.02956</v>
       </c>
       <c r="EU2" t="n">
-        <v>1782111867</v>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>WEDGE INDUSTRIAL CO LTD</t>
-        </is>
+        <v>1619693940</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>1619693940</v>
       </c>
       <c r="EW2" t="inlineStr"/>
     </row>
